--- a/장비리스트0202v3.xlsx
+++ b/장비리스트0202v3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jise0\OneDrive\문서\카카오톡 받은 파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevinkangm4/WORK/greenbell_1_0_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03DC01E4-1C3B-4547-944C-656ED06617AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651A9B10-E510-634D-A8AC-05A5F44ED8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="21800" windowHeight="16640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="152">
   <si>
     <t>c10</t>
   </si>
@@ -417,14 +417,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">내과(혈액검사장비) </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>영상검사장비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>외과</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -523,6 +515,15 @@
   <si>
     <t>마취장비</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INS028</t>
+  </si>
+  <si>
+    <t>INS029</t>
+  </si>
+  <si>
+    <t>INS030</t>
   </si>
 </sst>
 </file>
@@ -696,9 +697,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -736,7 +737,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -842,7 +843,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -984,7 +985,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -993,15 +994,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="17"/>
   <cols>
-    <col min="2" max="2" width="30.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="27.1875" customWidth="1"/>
-    <col min="4" max="4" width="47.0625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="35.3125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="30.5" style="3" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="27.1640625" customWidth="1"/>
+    <col min="4" max="4" width="47" style="3" customWidth="1"/>
+    <col min="5" max="5" width="35.33203125" style="3" customWidth="1"/>
     <col min="6" max="6" width="35" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.3125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.6875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="42.5" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1016,7 +1017,7 @@
         <v>123</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>122</v>
@@ -1043,10 +1044,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>100</v>
@@ -1073,10 +1074,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>99</v>
@@ -1096,13 +1097,13 @@
         <v>101</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>102</v>
@@ -1127,10 +1128,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>119</v>
@@ -1153,7 +1154,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="7" t="s">
@@ -1180,7 +1181,7 @@
         <v>125</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>4</v>
@@ -1200,16 +1201,16 @@
         <v>43</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>44</v>
@@ -1227,10 +1228,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>105</v>
@@ -1253,7 +1254,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
@@ -1277,10 +1278,10 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>108</v>
@@ -1303,10 +1304,10 @@
         <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>109</v>
@@ -1329,11 +1330,11 @@
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>54</v>
@@ -1351,13 +1352,13 @@
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>56</v>
@@ -1374,13 +1375,13 @@
         <v>58</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>59</v>
@@ -1403,10 +1404,10 @@
         <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>63</v>
@@ -1429,10 +1430,10 @@
         <v>12</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>66</v>
@@ -1455,7 +1456,7 @@
         <v>13</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
@@ -1477,7 +1478,7 @@
         <v>14</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
@@ -1501,7 +1502,7 @@
         <v>15</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
@@ -1525,7 +1526,7 @@
         <v>120</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -1547,10 +1548,10 @@
         <v>16</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>80</v>
@@ -1573,13 +1574,13 @@
         <v>17</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>84</v>
@@ -1599,10 +1600,10 @@
         <v>18</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
@@ -1620,13 +1621,13 @@
         <v>88</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>115</v>
@@ -1649,10 +1650,10 @@
         <v>19</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>116</v>
@@ -1675,10 +1676,10 @@
         <v>20</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>92</v>
@@ -1701,10 +1702,10 @@
         <v>21</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>118</v>
@@ -1719,7 +1720,29 @@
       </c>
       <c r="J28" s="1"/>
     </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
     <row r="31" spans="1:10">
+      <c r="A31" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="J31" s="1"/>
     </row>
     <row r="40" spans="2:5">

--- a/장비리스트0202v3.xlsx
+++ b/장비리스트0202v3.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevinkangm4/WORK/greenbell_1_0_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651A9B10-E510-634D-A8AC-05A5F44ED8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B98824-2FF9-C04D-82D1-3AA9788EFC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="21800" windowHeight="16640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2300" yWindow="1480" windowWidth="31860" windowHeight="16640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="152">
   <si>
     <t>c10</t>
   </si>
@@ -635,7 +636,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -678,6 +679,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1755,4 +1762,312 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75B9C2E-5163-1C44-A803-E9984A130466}">
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <cols>
+    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="16"/>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="1"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" s="1"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C30" s="1"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/장비리스트0202v3.xlsx
+++ b/장비리스트0202v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevinkangm4/WORK/greenbell_1_0_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B98824-2FF9-C04D-82D1-3AA9788EFC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544B1E73-27DE-424A-B313-A0B86EF5041F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2300" yWindow="1480" windowWidth="31860" windowHeight="16640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6800" yWindow="1840" windowWidth="10000" windowHeight="16640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -194,337 +194,338 @@
     <t>Veterinary Anesthesia Machine</t>
   </si>
   <si>
+    <t>INS014</t>
+  </si>
+  <si>
+    <t>Multi-parameter Patient Monitor</t>
+  </si>
+  <si>
+    <t>Magnific Touch</t>
+  </si>
+  <si>
+    <t>ANIAN</t>
+  </si>
+  <si>
+    <t>INS015</t>
+  </si>
+  <si>
+    <t>X-RAY GENERATOR</t>
+  </si>
+  <si>
+    <t>DG-S010V1</t>
+  </si>
+  <si>
+    <t>VATECH Co., Ltd.</t>
+  </si>
+  <si>
+    <t>의료용저온플라즈마멸균기</t>
+  </si>
+  <si>
+    <t>STERLINK lite+</t>
+  </si>
+  <si>
+    <t>(주)플라즈맵</t>
+  </si>
+  <si>
+    <t>N-200M</t>
+  </si>
+  <si>
+    <t>INS018</t>
+  </si>
+  <si>
+    <t>범용초음파영상진단장치</t>
+  </si>
+  <si>
+    <t>HS60</t>
+  </si>
+  <si>
+    <t>삼성에디슨</t>
+  </si>
+  <si>
+    <t>INS019</t>
+  </si>
+  <si>
+    <t>BLOOD FLOW DOPPER MOLDEL BF2</t>
+  </si>
+  <si>
+    <t>Vmed Technology</t>
+  </si>
+  <si>
+    <t>INS020</t>
+  </si>
+  <si>
+    <t>TH 9428 HP2H211VR13</t>
+  </si>
+  <si>
+    <t>THALES ELECTRON DEVICES</t>
+  </si>
+  <si>
+    <t>범용전기수술기</t>
+  </si>
+  <si>
+    <t>DOCTANZ 150</t>
+  </si>
+  <si>
+    <t>(주)제로원</t>
+  </si>
+  <si>
+    <t>INS022</t>
+  </si>
+  <si>
+    <t>Gaia a</t>
+  </si>
+  <si>
+    <t>HANMI LTD.</t>
+  </si>
+  <si>
+    <t>USG-410</t>
+  </si>
+  <si>
+    <t>OLYMPUS</t>
+  </si>
+  <si>
+    <t>INS024</t>
+  </si>
+  <si>
+    <t>Vetal 3</t>
+  </si>
+  <si>
+    <t>INS025</t>
+  </si>
+  <si>
+    <t>Veta 5</t>
+  </si>
+  <si>
+    <t>고압 증기 멸균기</t>
+  </si>
+  <si>
+    <t>S-410</t>
+  </si>
+  <si>
+    <t>(주)델타엠에스</t>
+  </si>
+  <si>
+    <t>INS027</t>
+  </si>
+  <si>
+    <t>IDEXX ProCyte Dx</t>
+  </si>
+  <si>
+    <t>INS001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INS002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동물용 혈액학검사장비</t>
+  </si>
+  <si>
+    <t>올인원 건식 생화학 카트리지</t>
+  </si>
+  <si>
+    <t>INS003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>환자감시장치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>형광면역분석 장비</t>
+  </si>
+  <si>
+    <t>INS006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호르몬혈액분석기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INS009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INS010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체외진단분석기</t>
+  </si>
+  <si>
+    <t>수의 혈액 화학 분석기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INS016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INS017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도플러 혈압계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INS021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INS023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생체 신호 모니터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동물용 마취기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INS026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>혈액분석기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C.T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c-arm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비명 홈피용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">구분 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>외과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내과, 외과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">설명 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">혈청검사장비 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">혈구검사장비 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동혈구분석장비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수술도구 멸균장비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">치과- 치과진단용 방사선장비 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스케일러- 스케일러아님.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>치과- 덴탈머신-모든 외과적 치과치료용 장비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마취시, 혹은 비마취시, 환축 생존 vital 상태 표시장비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>치과실모니터링-환축모니터링장비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마취모니터링-환축모니터링장비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ct모니터링-환축모니터링장비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>환축 모니터링기 (CT,치과실,마취 단어는 무시할것)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">수술시, 마취장비 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">수술시 지혈 을 위한 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">차별화 장비 . 내과 외과에 다 넣을것. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">내과 외과  전부 속함. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">IDEXX 사의 혈액검사장비 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스케일러-틀렸음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>치과실 마취기-틀렸음. 그냥마취장비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전해질,혈액가스분석기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마취장비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INS028</t>
+  </si>
+  <si>
+    <t>INS029</t>
+  </si>
+  <si>
+    <t>INS030</t>
+  </si>
+  <si>
     <t>Comen Medical Instruments Co., Ltd.</t>
-  </si>
-  <si>
-    <t>INS014</t>
-  </si>
-  <si>
-    <t>Multi-parameter Patient Monitor</t>
-  </si>
-  <si>
-    <t>Magnific Touch</t>
-  </si>
-  <si>
-    <t>ANIAN</t>
-  </si>
-  <si>
-    <t>INS015</t>
-  </si>
-  <si>
-    <t>X-RAY GENERATOR</t>
-  </si>
-  <si>
-    <t>DG-S010V1</t>
-  </si>
-  <si>
-    <t>VATECH Co., Ltd.</t>
-  </si>
-  <si>
-    <t>의료용저온플라즈마멸균기</t>
-  </si>
-  <si>
-    <t>STERLINK lite+</t>
-  </si>
-  <si>
-    <t>(주)플라즈맵</t>
-  </si>
-  <si>
-    <t>N-200M</t>
-  </si>
-  <si>
-    <t>INS018</t>
-  </si>
-  <si>
-    <t>범용초음파영상진단장치</t>
-  </si>
-  <si>
-    <t>HS60</t>
-  </si>
-  <si>
-    <t>삼성에디슨</t>
-  </si>
-  <si>
-    <t>INS019</t>
-  </si>
-  <si>
-    <t>BLOOD FLOW DOPPER MOLDEL BF2</t>
-  </si>
-  <si>
-    <t>Vmed Technology</t>
-  </si>
-  <si>
-    <t>INS020</t>
-  </si>
-  <si>
-    <t>TH 9428 HP2H211VR13</t>
-  </si>
-  <si>
-    <t>THALES ELECTRON DEVICES</t>
-  </si>
-  <si>
-    <t>범용전기수술기</t>
-  </si>
-  <si>
-    <t>DOCTANZ 150</t>
-  </si>
-  <si>
-    <t>(주)제로원</t>
-  </si>
-  <si>
-    <t>INS022</t>
-  </si>
-  <si>
-    <t>Gaia a</t>
-  </si>
-  <si>
-    <t>HANMI LTD.</t>
-  </si>
-  <si>
-    <t>USG-410</t>
-  </si>
-  <si>
-    <t>OLYMPUS</t>
-  </si>
-  <si>
-    <t>INS024</t>
-  </si>
-  <si>
-    <t>Vetal 3</t>
-  </si>
-  <si>
-    <t>INS025</t>
-  </si>
-  <si>
-    <t>Veta 5</t>
-  </si>
-  <si>
-    <t>고압 증기 멸균기</t>
-  </si>
-  <si>
-    <t>S-410</t>
-  </si>
-  <si>
-    <t>(주)델타엠에스</t>
-  </si>
-  <si>
-    <t>INS027</t>
-  </si>
-  <si>
-    <t>IDEXX ProCyte Dx</t>
-  </si>
-  <si>
-    <t>INS001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INS002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>동물용 혈액학검사장비</t>
-  </si>
-  <si>
-    <t>올인원 건식 생화학 카트리지</t>
-  </si>
-  <si>
-    <t>INS003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>환자감시장치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>형광면역분석 장비</t>
-  </si>
-  <si>
-    <t>INS006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>호르몬혈액분석기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INS009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INS010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>체외진단분석기</t>
-  </si>
-  <si>
-    <t>수의 혈액 화학 분석기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INS016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INS017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>도플러 혈압계</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INS021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INS023</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>생체 신호 모니터</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>동물용 마취기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INS026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>혈액분석기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C.T</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c-arm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>장비명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>장비명 홈피용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">구분 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>외과</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>내과, 외과</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>내과</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">설명 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">혈청검사장비 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">혈구검사장비 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>자동혈구분석장비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수술도구 멸균장비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">치과- 치과진단용 방사선장비 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스케일러- 스케일러아님.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>치과- 덴탈머신-모든 외과적 치과치료용 장비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마취시, 혹은 비마취시, 환축 생존 vital 상태 표시장비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>치과실모니터링-환축모니터링장비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마취모니터링-환축모니터링장비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ct모니터링-환축모니터링장비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>환축 모니터링기 (CT,치과실,마취 단어는 무시할것)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">수술시, 마취장비 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">수술시 지혈 을 위한 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">차별화 장비 . 내과 외과에 다 넣을것. </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">내과 외과  전부 속함. </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">IDEXX 사의 혈액검사장비 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스케일러-틀렸음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>치과실 마취기-틀렸음. 그냥마취장비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전해질,혈액가스분석기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마취장비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INS028</t>
-  </si>
-  <si>
-    <t>INS029</t>
-  </si>
-  <si>
-    <t>INS030</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1018,16 +1019,16 @@
         <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>23</v>
@@ -1045,19 +1046,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>27</v>
@@ -1075,19 +1076,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>31</v>
@@ -1101,19 +1102,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>33</v>
@@ -1135,13 +1136,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>37</v>
@@ -1161,11 +1162,11 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>40</v>
@@ -1179,16 +1180,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>4</v>
@@ -1208,16 +1209,16 @@
         <v>43</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>44</v>
@@ -1235,13 +1236,13 @@
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>46</v>
@@ -1255,13 +1256,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
@@ -1279,19 +1280,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>50</v>
@@ -1311,13 +1312,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>52</v>
@@ -1337,11 +1338,11 @@
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>54</v>
@@ -1359,13 +1360,13 @@
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>56</v>
@@ -1373,104 +1374,104 @@
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
       <c r="I14" s="4" t="s">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="J14" s="4"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
       <c r="I16" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
       <c r="I17" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -1479,168 +1480,168 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
       <c r="I20" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
       <c r="I21" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
       <c r="I23" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -1651,22 +1652,22 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
@@ -1677,48 +1678,48 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
@@ -1729,26 +1730,26 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J31" s="1"/>
     </row>
@@ -1777,37 +1778,37 @@
         <v>22</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C1" s="16"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1815,10 +1816,10 @@
         <v>36</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1826,19 +1827,19 @@
         <v>39</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1847,7 +1848,7 @@
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1855,27 +1856,27 @@
         <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C11" s="1"/>
     </row>
@@ -1884,7 +1885,7 @@
         <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C12" s="1"/>
     </row>
@@ -1893,7 +1894,7 @@
         <v>53</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="1"/>
     </row>
@@ -1903,163 +1904,163 @@
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C18" s="1"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C19" s="1"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C20" s="1"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C28" s="1"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C29" s="1"/>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C30" s="1"/>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C31" s="1"/>
     </row>
